--- a/SGC-CKN/Excel/aa40ba10-7b32-4206-a59c-b57df37d0ee4_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-1_D800_11-11-2026.xlsx
+++ b/SGC-CKN/Excel/aa40ba10-7b32-4206-a59c-b57df37d0ee4_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-1_D800_11-11-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:50 06/11/2026</t>
+    <t>15/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:10 11/11/2026</t>
+    <t>14/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
